--- a/mistral_translate_work/split_by_prompt/excel/story_dialogue/lang_multi_text/lang_multi_text__story_dialogue__part_0131.xlsx
+++ b/mistral_translate_work/split_by_prompt/excel/story_dialogue/lang_multi_text/lang_multi_text__story_dialogue__part_0131.xlsx
@@ -28134,7 +28134,7 @@
       </c>
       <c r="M426" t="inlineStr">
         <is>
-          <t>"Nhưng Linnea đã nói dối! Barton thấy cô ấy treo tấm chăn lên cành cây sâu trong Rừng Bjartr cơ. Cô ấy đâu có đưa cho ai trong tộc Soliskin đâu."</t>
+          <t>"Nhưng Linnea đã nói dối! Barton thấy cô ấy treo tấm chăn lên cành cây sâu trong Bjartr Woods cơ. Cô ấy đâu có đưa cho ai trong tộc Soliskin đâu."</t>
         </is>
       </c>
     </row>
@@ -29434,7 +29434,7 @@
       </c>
       <c r="M446" t="inlineStr">
         <is>
-          <t>Ta đã bảo rồi, "Đi với nhóm Học viện. Đừng có đi lang thang một mình." Budee, sao ngươi không chịu nghe thế?!</t>
+          <t>Tao đã bảo rồi, "Đi với nhóm Học viện. Đừng có đi lang thang một mình." Budee, sao mày không chịu nghe thế?!</t>
         </is>
       </c>
     </row>
@@ -29824,7 +29824,7 @@
       </c>
       <c r="M452" t="inlineStr">
         <is>
-          <t>ĐỢI Ta ĐÃ, BUDEE!!!</t>
+          <t>ĐỢI TAO ĐÃ, BUDEE!!!</t>
         </is>
       </c>
     </row>
@@ -30409,7 +30409,7 @@
       </c>
       <c r="M461" t="inlineStr">
         <is>
-          <t>Nó nắm địa hình như lòng bàn tay và dẫn ta qua biết bao lối tắt. Cuối cùng, nó còn đánh lạc hướng Exoswarm để ta có thể thoát thân.</t>
+          <t>Nó nắm địa hình như lòng bàn tay và dẫn tao qua biết bao lối tắt. Cuối cùng, nó còn đánh lạc hướng Exoswarm để tao có thể thoát thân.</t>
         </is>
       </c>
     </row>
@@ -30994,7 +30994,7 @@
       </c>
       <c r="M470" t="inlineStr">
         <is>
-          <t>"Nếu Linnea ở lại Lahai-Roi vì chúng ta, thì có lẽ việc nhìn thấy thế giới bên ngoài sẽ khiến ngươi vui." Đó là những gì nó nói với ta.</t>
+          <t>"Nếu Linnea ở lại Lahai-Roi vì chúng ta, thì có lẽ việc nhìn thấy thế giới bên ngoài sẽ khiến mày vui." Đó là những gì nó nói với tao.</t>
         </is>
       </c>
     </row>
